--- a/03_test-cases/v1.0/fragments/TC-TANGQUA-v1.0.xlsx
+++ b/03_test-cases/v1.0/fragments/TC-TANGQUA-v1.0.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Test Cases" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Tặng quà" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Coverage Matrix" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>

--- a/03_test-cases/v1.0/fragments/TC-TANGQUA-v1.0.xlsx
+++ b/03_test-cases/v1.0/fragments/TC-TANGQUA-v1.0.xlsx
@@ -4,14 +4,14 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Tặng quà" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Coverage Matrix" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Test Cases'!$A$6:$U$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Tặng quà'!$A$6:$U$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Coverage Matrix'!$A$1:$M$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -2587,14 +2587,14 @@
           <t>Tặng quà</t>
         </is>
       </c>
-      <c r="B7" s="227" t="n"/>
-      <c r="C7" s="227" t="n"/>
-      <c r="D7" s="227" t="n"/>
-      <c r="E7" s="227" t="n"/>
-      <c r="F7" s="227" t="n"/>
-      <c r="G7" s="227" t="n"/>
-      <c r="H7" s="227" t="n"/>
-      <c r="I7" s="228" t="n"/>
+      <c r="B7" s="211" t="n"/>
+      <c r="C7" s="211" t="n"/>
+      <c r="D7" s="211" t="n"/>
+      <c r="E7" s="211" t="n"/>
+      <c r="F7" s="211" t="n"/>
+      <c r="G7" s="211" t="n"/>
+      <c r="H7" s="211" t="n"/>
+      <c r="I7" s="209" t="n"/>
       <c r="J7" s="229" t="n"/>
       <c r="K7" s="229" t="n"/>
       <c r="L7" s="229" t="n"/>
@@ -2636,13 +2636,13 @@
           <t>Block Lối vào — Nút "Cảm ơn người vận chuyển" tại Theo dõi đơn</t>
         </is>
       </c>
-      <c r="C8" s="233" t="n"/>
-      <c r="D8" s="233" t="n"/>
-      <c r="E8" s="233" t="n"/>
-      <c r="F8" s="233" t="n"/>
-      <c r="G8" s="233" t="n"/>
-      <c r="H8" s="233" t="n"/>
-      <c r="I8" s="234" t="n"/>
+      <c r="C8" s="211" t="n"/>
+      <c r="D8" s="211" t="n"/>
+      <c r="E8" s="211" t="n"/>
+      <c r="F8" s="211" t="n"/>
+      <c r="G8" s="211" t="n"/>
+      <c r="H8" s="211" t="n"/>
+      <c r="I8" s="209" t="n"/>
       <c r="J8" s="231" t="n"/>
       <c r="K8" s="231" t="n"/>
       <c r="L8" s="231" t="n"/>
@@ -2689,7 +2689,7 @@
       </c>
       <c r="C9" s="239" t="inlineStr">
         <is>
-          <t>Quan sát thực tế app STG + ảnh DOC-v1.0-04 (ma trận nhãn nút)</t>
+          <t>DOC-v1.0-04 + DOC-v1.0-05</t>
         </is>
       </c>
       <c r="D9" s="239" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="C10" s="239" t="inlineStr">
         <is>
-          <t>Quan sát thực tế app STG + ảnh DOC-v1.0-04 (ma trận nhãn nút)</t>
+          <t>DOC-v1.0-04 + DOC-v1.0-05</t>
         </is>
       </c>
       <c r="D10" s="239" t="inlineStr">
@@ -2892,13 +2892,13 @@
           <t>Block Màn Tặng quà — 4 lựa chọn quà</t>
         </is>
       </c>
-      <c r="C11" s="233" t="n"/>
-      <c r="D11" s="233" t="n"/>
-      <c r="E11" s="233" t="n"/>
-      <c r="F11" s="233" t="n"/>
-      <c r="G11" s="233" t="n"/>
-      <c r="H11" s="233" t="n"/>
-      <c r="I11" s="234" t="n"/>
+      <c r="C11" s="211" t="n"/>
+      <c r="D11" s="211" t="n"/>
+      <c r="E11" s="211" t="n"/>
+      <c r="F11" s="211" t="n"/>
+      <c r="G11" s="211" t="n"/>
+      <c r="H11" s="211" t="n"/>
+      <c r="I11" s="209" t="n"/>
       <c r="J11" s="231" t="n"/>
       <c r="K11" s="231" t="n"/>
       <c r="L11" s="231" t="n"/>
@@ -2945,7 +2945,7 @@
       </c>
       <c r="C12" s="239" t="inlineStr">
         <is>
-          <t>DOC-v1.0-01 §D3/§D4 (GIFT-01, BR-GIFT-01) + DOC-v1.0-02 §3.8 + ảnh DOC-v1.0-04</t>
+          <t>Quan sát thực tế app STG (QA GiangDC2, chat 2026-07-30)</t>
         </is>
       </c>
       <c r="D12" s="239" t="inlineStr">
@@ -2955,29 +2955,30 @@
       </c>
       <c r="E12" s="239" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="F12" s="239" t="inlineStr">
         <is>
-          <t>Check đầy đủ + đúng 5 thành phần hiển thị tại màn Tặng quà</t>
+          <t>Check icon quay lại tại màn Tặng quà</t>
         </is>
       </c>
       <c r="G12" s="239" t="inlineStr">
         <is>
-          <t>Đơn đã "Hoàn thành", Sender vừa mở màn Tặng quà và chưa chọn loại quà nào</t>
+          <t>Đơn đã chuyển "Hoàn thành", user đăng nhập là Sender</t>
         </is>
       </c>
       <c r="H12" s="239" t="inlineStr">
         <is>
-          <t>1. Mở app FoxEco bằng tài khoản Người gửi (Sender)
-2. Bấm tab "Hoạt động", mở đơn đã "Hoàn thành" để vào màn "Theo dõi đơn", bấm "✓ Cảm ơn người vận chuyển"
-3. Quan sát toàn bộ màn Tặng quà từ trên xuống dưới</t>
+          <t>1. Mở app FoxEco bằng tài khoản Sender
+2. Bấm tab "Hoạt động" → mở đơn đã "Hoàn thành" → vào màn Theo dõi đơn
+3. Bấm "Cảm ơn người vận chuyển" để mở màn Tặng quà
+4. Bấm icon quay lại (←) ở Header</t>
         </is>
       </c>
       <c r="I12" s="239" t="inlineStr">
         <is>
-          <t>3. Màn hiển thị đủ 5 thành phần: (1) title "Tặng quà", (2) nội dung mở đầu "Hành trình hoàn thành!" / "Gửi một món quà cảm ơn người vận chuyển", (3) label "Chọn một món quà gửi tặng người vận chuyển", (4) 4 chip lựa chọn quà, (5) nút "✓ Xác nhận tặng quà"</t>
+          <t>4. Điều hướng đúng về màn Theo dõi đơn</t>
         </is>
       </c>
       <c r="J12" s="239" t="inlineStr">
@@ -3022,20 +3023,20 @@
       <c r="AK12" s="240" t="n"/>
       <c r="AL12" s="240" t="n"/>
       <c r="AM12" s="241">
-        <f>IF($A12="","",IF(OR($N12="Yes",$S12="Yes",$X12="Yes",$AC12="Yes",$AH12="Yes"),"Yes","No"))</f>
+        <f>IF($A10="","",IF(OR($N10="Yes",$S10="Yes",$X10="Yes",$AC10="Yes",$AH10="Yes"),"Yes","No"))</f>
         <v/>
       </c>
       <c r="AN12" s="241">
-        <f>IF($A12="","",IFERROR(IF($AI12&lt;&gt;"",$AI12,IF($AD12&lt;&gt;"",$AD12,IF($Y12&lt;&gt;"",$Y12,IF($T12&lt;&gt;"",$T12,IF($O12&lt;&gt;"",$O12,""))))),""))</f>
+        <f>IF($A10="","",IFERROR(IF($AI10&lt;&gt;"",$AI10,IF($AD10&lt;&gt;"",$AD10,IF($Y10&lt;&gt;"",$Y10,IF($T10&lt;&gt;"",$T10,IF($O10&lt;&gt;"",$O10,""))))),""))</f>
         <v/>
       </c>
       <c r="AO12" s="241">
-        <f>IFERROR(IF($AJ12&lt;&gt;"",$AJ12,IF($AE12&lt;&gt;"",$AE12,IF($Z12&lt;&gt;"",$Z12,IF($U12&lt;&gt;"",$U12,IF($P12&lt;&gt;"",$P12,""))))),"")</f>
+        <f>IFERROR(IF($AJ10&lt;&gt;"",$AJ10,IF($AE10&lt;&gt;"",$AE10,IF($Z10&lt;&gt;"",$Z10,IF($U10&lt;&gt;"",$U10,IF($P10&lt;&gt;"",$P10,""))))),"")</f>
         <v/>
       </c>
       <c r="AP12" s="240" t="inlineStr">
         <is>
-          <t>Field/column completeness check — auto-derived (xem generate.md Step 3b) | Text verbatim xác nhận qua ảnh Figma DOC-v1.0-04 (hash 5d29d082…, 165aaa39…). KHÔNG assert phần chấm sao 1-5 (`REQ-GIFT-002`/RAT-01/02) — C-GIFT-01 Resolved: rating là phase sau, out of scope v1.0; màn Tặng quà xác nhận KHÔNG có UI sao</t>
+          <t>Technique: EP-back-icon. Bổ sung 2026-07-30 theo yêu cầu user (QA GiangDC2 xác nhận trực tiếp trên app STG: icon quay lại tồn tại và hoạt động đúng ở màn này) — phát hiện khi quét lại toàn bộ TC-MASTER, kiểm tra completeness icon Back cho từng màn hình.</t>
         </is>
       </c>
     </row>
@@ -3066,24 +3067,24 @@
       </c>
       <c r="F13" s="239" t="inlineStr">
         <is>
-          <t>Check đủ 4 chip loại quà hiển thị đúng nhãn tại màn Tặng quà</t>
+          <t>Check đầy đủ + đúng 5 thành phần hiển thị tại màn Tặng quà</t>
         </is>
       </c>
       <c r="G13" s="239" t="inlineStr">
         <is>
-          <t>Đơn đã "Hoàn thành", Sender vừa mở màn Tặng quà</t>
+          <t>Đơn đã "Hoàn thành", Sender vừa mở màn Tặng quà và chưa chọn loại quà nào</t>
         </is>
       </c>
       <c r="H13" s="239" t="inlineStr">
         <is>
           <t>1. Mở app FoxEco bằng tài khoản Người gửi (Sender)
 2. Bấm tab "Hoạt động", mở đơn đã "Hoàn thành" để vào màn "Theo dõi đơn", bấm "✓ Cảm ơn người vận chuyển"
-3. Quan sát danh sách chip lựa chọn quà</t>
+3. Quan sát toàn bộ màn Tặng quà từ trên xuống dưới</t>
         </is>
       </c>
       <c r="I13" s="239" t="inlineStr">
         <is>
-          <t>3. Hiển thị đủ 4 chip đúng nhãn theo thứ tự: "🌷 Bông hoa", "☕ Ly cà phê", "🧸 Gấu bông", "👑 Vương miện" — không thiếu, không thừa loại nào</t>
+          <t>3. Màn hiển thị đủ 5 thành phần: (1) title "Tặng quà", (2) nội dung mở đầu "Hành trình hoàn thành!" / "Gửi một món quà cảm ơn người vận chuyển", (3) label "Chọn một món quà gửi tặng người vận chuyển", (4) 4 chip lựa chọn quà, (5) nút "✓ Xác nhận tặng quà"</t>
         </is>
       </c>
       <c r="J13" s="239" t="inlineStr">
@@ -3128,20 +3129,20 @@
       <c r="AK13" s="240" t="n"/>
       <c r="AL13" s="240" t="n"/>
       <c r="AM13" s="241">
-        <f>IF($A13="","",IF(OR($N13="Yes",$S13="Yes",$X13="Yes",$AC13="Yes",$AH13="Yes"),"Yes","No"))</f>
+        <f>IF($A12="","",IF(OR($N12="Yes",$S12="Yes",$X12="Yes",$AC12="Yes",$AH12="Yes"),"Yes","No"))</f>
         <v/>
       </c>
       <c r="AN13" s="241">
-        <f>IF($A13="","",IFERROR(IF($AI13&lt;&gt;"",$AI13,IF($AD13&lt;&gt;"",$AD13,IF($Y13&lt;&gt;"",$Y13,IF($T13&lt;&gt;"",$T13,IF($O13&lt;&gt;"",$O13,""))))),""))</f>
+        <f>IF($A12="","",IFERROR(IF($AI12&lt;&gt;"",$AI12,IF($AD12&lt;&gt;"",$AD12,IF($Y12&lt;&gt;"",$Y12,IF($T12&lt;&gt;"",$T12,IF($O12&lt;&gt;"",$O12,""))))),""))</f>
         <v/>
       </c>
       <c r="AO13" s="241">
-        <f>IFERROR(IF($AJ13&lt;&gt;"",$AJ13,IF($AE13&lt;&gt;"",$AE13,IF($Z13&lt;&gt;"",$Z13,IF($U13&lt;&gt;"",$U13,IF($P13&lt;&gt;"",$P13,""))))),"")</f>
+        <f>IFERROR(IF($AJ12&lt;&gt;"",$AJ12,IF($AE12&lt;&gt;"",$AE12,IF($Z12&lt;&gt;"",$Z12,IF($U12&lt;&gt;"",$U12,IF($P12&lt;&gt;"",$P12,""))))),"")</f>
         <v/>
       </c>
       <c r="AP13" s="240" t="inlineStr">
         <is>
-          <t>Field/column completeness check — auto-derived (xem generate.md Step 3b)</t>
+          <t>Field/column completeness check — auto-derived (xem generate.md Step 3b) | Text verbatim xác nhận qua ảnh Figma DOC-v1.0-04 (hash 5d29d082…, 165aaa39…). KHÔNG assert phần chấm sao 1-5 (`REQ-GIFT-002`/RAT-01/02) — C-GIFT-01 Resolved: rating là phase sau, out of scope v1.0; màn Tặng quà xác nhận KHÔNG có UI sao</t>
         </is>
       </c>
     </row>
@@ -3162,7 +3163,7 @@
       </c>
       <c r="D14" s="239" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="E14" s="239" t="inlineStr">
@@ -3172,24 +3173,24 @@
       </c>
       <c r="F14" s="239" t="inlineStr">
         <is>
-          <t>Check chọn quà "🌷 Bông hoa" hiển thị đúng trạng thái đã chọn</t>
+          <t>Check đủ 4 chip loại quà hiển thị đúng nhãn tại màn Tặng quà</t>
         </is>
       </c>
       <c r="G14" s="239" t="inlineStr">
         <is>
-          <t>Đang ở màn Tặng quà, chưa chọn loại quà nào</t>
+          <t>Đơn đã "Hoàn thành", Sender vừa mở màn Tặng quà</t>
         </is>
       </c>
       <c r="H14" s="239" t="inlineStr">
         <is>
           <t>1. Mở app FoxEco bằng tài khoản Người gửi (Sender)
 2. Bấm tab "Hoạt động", mở đơn đã "Hoàn thành" để vào màn "Theo dõi đơn", bấm "✓ Cảm ơn người vận chuyển"
-3. Bấm chip "🌷 Bông hoa"</t>
+3. Quan sát danh sách chip lựa chọn quà</t>
         </is>
       </c>
       <c r="I14" s="239" t="inlineStr">
         <is>
-          <t>3. Chip "🌷 Bông hoa" chuyển sang trạng thái đã chọn (có viền cam); nút "✓ Xác nhận tặng quà" sẵn sàng gửi</t>
+          <t>3. Hiển thị đủ 4 chip đúng nhãn theo thứ tự: "🌷 Bông hoa", "☕ Ly cà phê", "🧸 Gấu bông", "👑 Vương miện" — không thiếu, không thừa loại nào</t>
         </is>
       </c>
       <c r="J14" s="239" t="inlineStr">
@@ -3234,20 +3235,20 @@
       <c r="AK14" s="240" t="n"/>
       <c r="AL14" s="240" t="n"/>
       <c r="AM14" s="241">
-        <f>IF($A14="","",IF(OR($N14="Yes",$S14="Yes",$X14="Yes",$AC14="Yes",$AH14="Yes"),"Yes","No"))</f>
+        <f>IF($A13="","",IF(OR($N13="Yes",$S13="Yes",$X13="Yes",$AC13="Yes",$AH13="Yes"),"Yes","No"))</f>
         <v/>
       </c>
       <c r="AN14" s="241">
-        <f>IF($A14="","",IFERROR(IF($AI14&lt;&gt;"",$AI14,IF($AD14&lt;&gt;"",$AD14,IF($Y14&lt;&gt;"",$Y14,IF($T14&lt;&gt;"",$T14,IF($O14&lt;&gt;"",$O14,""))))),""))</f>
+        <f>IF($A13="","",IFERROR(IF($AI13&lt;&gt;"",$AI13,IF($AD13&lt;&gt;"",$AD13,IF($Y13&lt;&gt;"",$Y13,IF($T13&lt;&gt;"",$T13,IF($O13&lt;&gt;"",$O13,""))))),""))</f>
         <v/>
       </c>
       <c r="AO14" s="241">
-        <f>IFERROR(IF($AJ14&lt;&gt;"",$AJ14,IF($AE14&lt;&gt;"",$AE14,IF($Z14&lt;&gt;"",$Z14,IF($U14&lt;&gt;"",$U14,IF($P14&lt;&gt;"",$P14,""))))),"")</f>
+        <f>IFERROR(IF($AJ13&lt;&gt;"",$AJ13,IF($AE13&lt;&gt;"",$AE13,IF($Z13&lt;&gt;"",$Z13,IF($U13&lt;&gt;"",$U13,IF($P13&lt;&gt;"",$P13,""))))),"")</f>
         <v/>
       </c>
       <c r="AP14" s="240" t="inlineStr">
         <is>
-          <t>Technique: EP-flower</t>
+          <t>Field/column completeness check — auto-derived (xem generate.md Step 3b)</t>
         </is>
       </c>
     </row>
@@ -3256,46 +3257,46 @@
         <f>IF(C15="","",$C$2&amp;"."&amp;COUNTA($C$8:C15)&amp;"")</f>
         <v/>
       </c>
-      <c r="B15" s="243" t="inlineStr">
+      <c r="B15" s="239" t="inlineStr">
         <is>
           <t>REQ-GIFT-001</t>
         </is>
       </c>
-      <c r="C15" s="244" t="inlineStr">
+      <c r="C15" s="239" t="inlineStr">
         <is>
           <t>DOC-v1.0-01 §D3/§D4 (GIFT-01, BR-GIFT-01) + DOC-v1.0-02 §3.8 + ảnh DOC-v1.0-04</t>
         </is>
       </c>
-      <c r="D15" s="244" t="inlineStr">
+      <c r="D15" s="239" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="E15" s="244" t="inlineStr">
+      <c r="E15" s="239" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F15" s="244" t="inlineStr">
-        <is>
-          <t>Check chọn quà "☕ Ly cà phê" hiển thị đúng trạng thái đã chọn</t>
-        </is>
-      </c>
-      <c r="G15" s="244" t="inlineStr">
+      <c r="F15" s="239" t="inlineStr">
+        <is>
+          <t>Check chọn quà "🌷 Bông hoa" hiển thị đúng trạng thái đã chọn</t>
+        </is>
+      </c>
+      <c r="G15" s="239" t="inlineStr">
         <is>
           <t>Đang ở màn Tặng quà, chưa chọn loại quà nào</t>
         </is>
       </c>
-      <c r="H15" s="244" t="inlineStr">
+      <c r="H15" s="239" t="inlineStr">
         <is>
           <t>1. Mở app FoxEco bằng tài khoản Người gửi (Sender)
 2. Bấm tab "Hoạt động", mở đơn đã "Hoàn thành" để vào màn "Theo dõi đơn", bấm "✓ Cảm ơn người vận chuyển"
-3. Bấm chip "☕ Ly cà phê"</t>
-        </is>
-      </c>
-      <c r="I15" s="244" t="inlineStr">
-        <is>
-          <t>3. Chip "☕ Ly cà phê" chuyển sang trạng thái đã chọn (có viền cam); nút "✓ Xác nhận tặng quà" sẵn sàng gửi</t>
+3. Bấm chip "🌷 Bông hoa"</t>
+        </is>
+      </c>
+      <c r="I15" s="239" t="inlineStr">
+        <is>
+          <t>3. Chip "🌷 Bông hoa" chuyển sang trạng thái đã chọn (có viền cam); nút "✓ Xác nhận tặng quà" sẵn sàng gửi</t>
         </is>
       </c>
       <c r="J15" s="239" t="inlineStr">
@@ -3340,20 +3341,20 @@
       <c r="AK15" s="240" t="n"/>
       <c r="AL15" s="240" t="n"/>
       <c r="AM15" s="241">
-        <f>IF($A15="","",IF(OR($N15="Yes",$S15="Yes",$X15="Yes",$AC15="Yes",$AH15="Yes"),"Yes","No"))</f>
+        <f>IF($A14="","",IF(OR($N14="Yes",$S14="Yes",$X14="Yes",$AC14="Yes",$AH14="Yes"),"Yes","No"))</f>
         <v/>
       </c>
       <c r="AN15" s="241">
-        <f>IF($A15="","",IFERROR(IF($AI15&lt;&gt;"",$AI15,IF($AD15&lt;&gt;"",$AD15,IF($Y15&lt;&gt;"",$Y15,IF($T15&lt;&gt;"",$T15,IF($O15&lt;&gt;"",$O15,""))))),""))</f>
+        <f>IF($A14="","",IFERROR(IF($AI14&lt;&gt;"",$AI14,IF($AD14&lt;&gt;"",$AD14,IF($Y14&lt;&gt;"",$Y14,IF($T14&lt;&gt;"",$T14,IF($O14&lt;&gt;"",$O14,""))))),""))</f>
         <v/>
       </c>
       <c r="AO15" s="241">
-        <f>IFERROR(IF($AJ15&lt;&gt;"",$AJ15,IF($AE15&lt;&gt;"",$AE15,IF($Z15&lt;&gt;"",$Z15,IF($U15&lt;&gt;"",$U15,IF($P15&lt;&gt;"",$P15,""))))),"")</f>
+        <f>IFERROR(IF($AJ14&lt;&gt;"",$AJ14,IF($AE14&lt;&gt;"",$AE14,IF($Z14&lt;&gt;"",$Z14,IF($U14&lt;&gt;"",$U14,IF($P14&lt;&gt;"",$P14,""))))),"")</f>
         <v/>
       </c>
       <c r="AP15" s="240" t="inlineStr">
         <is>
-          <t>Technique: EP-coffee</t>
+          <t>Technique: EP-flower</t>
         </is>
       </c>
     </row>
@@ -3362,46 +3363,46 @@
         <f>IF(C16="","",$C$2&amp;"."&amp;COUNTA($C$8:C16)&amp;"")</f>
         <v/>
       </c>
-      <c r="B16" s="239" t="inlineStr">
+      <c r="B16" s="243" t="inlineStr">
         <is>
           <t>REQ-GIFT-001</t>
         </is>
       </c>
-      <c r="C16" s="239" t="inlineStr">
+      <c r="C16" s="244" t="inlineStr">
         <is>
           <t>DOC-v1.0-01 §D3/§D4 (GIFT-01, BR-GIFT-01) + DOC-v1.0-02 §3.8 + ảnh DOC-v1.0-04</t>
         </is>
       </c>
-      <c r="D16" s="239" t="inlineStr">
+      <c r="D16" s="244" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="E16" s="239" t="inlineStr">
+      <c r="E16" s="244" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F16" s="239" t="inlineStr">
-        <is>
-          <t>Check chọn quà "🧸 Gấu bông" hiển thị đúng trạng thái đã chọn</t>
-        </is>
-      </c>
-      <c r="G16" s="239" t="inlineStr">
+      <c r="F16" s="244" t="inlineStr">
+        <is>
+          <t>Check chọn quà "☕ Ly cà phê" hiển thị đúng trạng thái đã chọn</t>
+        </is>
+      </c>
+      <c r="G16" s="244" t="inlineStr">
         <is>
           <t>Đang ở màn Tặng quà, chưa chọn loại quà nào</t>
         </is>
       </c>
-      <c r="H16" s="239" t="inlineStr">
+      <c r="H16" s="244" t="inlineStr">
         <is>
           <t>1. Mở app FoxEco bằng tài khoản Người gửi (Sender)
 2. Bấm tab "Hoạt động", mở đơn đã "Hoàn thành" để vào màn "Theo dõi đơn", bấm "✓ Cảm ơn người vận chuyển"
-3. Bấm chip "🧸 Gấu bông"</t>
-        </is>
-      </c>
-      <c r="I16" s="239" t="inlineStr">
-        <is>
-          <t>3. Chip "🧸 Gấu bông" chuyển sang trạng thái đã chọn (có viền cam); nút "✓ Xác nhận tặng quà" sẵn sàng gửi</t>
+3. Bấm chip "☕ Ly cà phê"</t>
+        </is>
+      </c>
+      <c r="I16" s="244" t="inlineStr">
+        <is>
+          <t>3. Chip "☕ Ly cà phê" chuyển sang trạng thái đã chọn (có viền cam); nút "✓ Xác nhận tặng quà" sẵn sàng gửi</t>
         </is>
       </c>
       <c r="J16" s="239" t="inlineStr">
@@ -3446,20 +3447,20 @@
       <c r="AK16" s="240" t="n"/>
       <c r="AL16" s="240" t="n"/>
       <c r="AM16" s="241">
-        <f>IF($A16="","",IF(OR($N16="Yes",$S16="Yes",$X16="Yes",$AC16="Yes",$AH16="Yes"),"Yes","No"))</f>
+        <f>IF($A15="","",IF(OR($N15="Yes",$S15="Yes",$X15="Yes",$AC15="Yes",$AH15="Yes"),"Yes","No"))</f>
         <v/>
       </c>
       <c r="AN16" s="241">
-        <f>IF($A16="","",IFERROR(IF($AI16&lt;&gt;"",$AI16,IF($AD16&lt;&gt;"",$AD16,IF($Y16&lt;&gt;"",$Y16,IF($T16&lt;&gt;"",$T16,IF($O16&lt;&gt;"",$O16,""))))),""))</f>
+        <f>IF($A15="","",IFERROR(IF($AI15&lt;&gt;"",$AI15,IF($AD15&lt;&gt;"",$AD15,IF($Y15&lt;&gt;"",$Y15,IF($T15&lt;&gt;"",$T15,IF($O15&lt;&gt;"",$O15,""))))),""))</f>
         <v/>
       </c>
       <c r="AO16" s="241">
-        <f>IFERROR(IF($AJ16&lt;&gt;"",$AJ16,IF($AE16&lt;&gt;"",$AE16,IF($Z16&lt;&gt;"",$Z16,IF($U16&lt;&gt;"",$U16,IF($P16&lt;&gt;"",$P16,""))))),"")</f>
+        <f>IFERROR(IF($AJ15&lt;&gt;"",$AJ15,IF($AE15&lt;&gt;"",$AE15,IF($Z15&lt;&gt;"",$Z15,IF($U15&lt;&gt;"",$U15,IF($P15&lt;&gt;"",$P15,""))))),"")</f>
         <v/>
       </c>
       <c r="AP16" s="240" t="inlineStr">
         <is>
-          <t>Technique: EP-teddy</t>
+          <t>Technique: EP-coffee</t>
         </is>
       </c>
     </row>
@@ -3490,7 +3491,7 @@
       </c>
       <c r="F17" s="239" t="inlineStr">
         <is>
-          <t>Check chọn quà "👑 Vương miện" hiển thị đúng trạng thái đã chọn</t>
+          <t>Check chọn quà "🧸 Gấu bông" hiển thị đúng trạng thái đã chọn</t>
         </is>
       </c>
       <c r="G17" s="239" t="inlineStr">
@@ -3502,12 +3503,12 @@
         <is>
           <t>1. Mở app FoxEco bằng tài khoản Người gửi (Sender)
 2. Bấm tab "Hoạt động", mở đơn đã "Hoàn thành" để vào màn "Theo dõi đơn", bấm "✓ Cảm ơn người vận chuyển"
-3. Bấm chip "👑 Vương miện"</t>
+3. Bấm chip "🧸 Gấu bông"</t>
         </is>
       </c>
       <c r="I17" s="239" t="inlineStr">
         <is>
-          <t>3. Chip "👑 Vương miện" chuyển sang trạng thái đã chọn (có viền cam); nút "✓ Xác nhận tặng quà" sẵn sàng gửi</t>
+          <t>3. Chip "🧸 Gấu bông" chuyển sang trạng thái đã chọn (có viền cam); nút "✓ Xác nhận tặng quà" sẵn sàng gửi</t>
         </is>
       </c>
       <c r="J17" s="239" t="inlineStr">
@@ -3552,430 +3553,434 @@
       <c r="AK17" s="240" t="n"/>
       <c r="AL17" s="240" t="n"/>
       <c r="AM17" s="241">
+        <f>IF($A16="","",IF(OR($N16="Yes",$S16="Yes",$X16="Yes",$AC16="Yes",$AH16="Yes"),"Yes","No"))</f>
+        <v/>
+      </c>
+      <c r="AN17" s="241">
+        <f>IF($A16="","",IFERROR(IF($AI16&lt;&gt;"",$AI16,IF($AD16&lt;&gt;"",$AD16,IF($Y16&lt;&gt;"",$Y16,IF($T16&lt;&gt;"",$T16,IF($O16&lt;&gt;"",$O16,""))))),""))</f>
+        <v/>
+      </c>
+      <c r="AO17" s="241">
+        <f>IFERROR(IF($AJ16&lt;&gt;"",$AJ16,IF($AE16&lt;&gt;"",$AE16,IF($Z16&lt;&gt;"",$Z16,IF($U16&lt;&gt;"",$U16,IF($P16&lt;&gt;"",$P16,""))))),"")</f>
+        <v/>
+      </c>
+      <c r="AP17" s="240" t="inlineStr">
+        <is>
+          <t>Technique: EP-teddy</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="60" customHeight="1" s="206">
+      <c r="A18" s="239">
+        <f>IF(C18="","",$C$2&amp;"."&amp;COUNTA($C$8:C18)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="B18" s="239" t="inlineStr">
+        <is>
+          <t>REQ-GIFT-001</t>
+        </is>
+      </c>
+      <c r="C18" s="239" t="inlineStr">
+        <is>
+          <t>DOC-v1.0-01 §D3/§D4 (GIFT-01, BR-GIFT-01) + DOC-v1.0-02 §3.8 + ảnh DOC-v1.0-04</t>
+        </is>
+      </c>
+      <c r="D18" s="239" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E18" s="239" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F18" s="239" t="inlineStr">
+        <is>
+          <t>Check chọn quà "👑 Vương miện" hiển thị đúng trạng thái đã chọn</t>
+        </is>
+      </c>
+      <c r="G18" s="239" t="inlineStr">
+        <is>
+          <t>Đang ở màn Tặng quà, chưa chọn loại quà nào</t>
+        </is>
+      </c>
+      <c r="H18" s="239" t="inlineStr">
+        <is>
+          <t>1. Mở app FoxEco bằng tài khoản Người gửi (Sender)
+2. Bấm tab "Hoạt động", mở đơn đã "Hoàn thành" để vào màn "Theo dõi đơn", bấm "✓ Cảm ơn người vận chuyển"
+3. Bấm chip "👑 Vương miện"</t>
+        </is>
+      </c>
+      <c r="I18" s="239" t="inlineStr">
+        <is>
+          <t>3. Chip "👑 Vương miện" chuyển sang trạng thái đã chọn (có viền cam); nút "✓ Xác nhận tặng quà" sẵn sàng gửi</t>
+        </is>
+      </c>
+      <c r="J18" s="239" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="K18" s="239" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="L18" s="239" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M18" s="239" t="n"/>
+      <c r="N18" s="239" t="n"/>
+      <c r="O18" s="239" t="n"/>
+      <c r="P18" s="239" t="n"/>
+      <c r="Q18" s="239" t="n"/>
+      <c r="R18" s="239" t="n"/>
+      <c r="S18" s="239" t="n"/>
+      <c r="T18" s="239" t="n"/>
+      <c r="U18" s="239" t="n"/>
+      <c r="V18" s="239" t="n"/>
+      <c r="W18" s="239" t="n"/>
+      <c r="X18" s="239" t="n"/>
+      <c r="Y18" s="239" t="n"/>
+      <c r="Z18" s="239" t="n"/>
+      <c r="AA18" s="239" t="n"/>
+      <c r="AB18" s="240" t="n"/>
+      <c r="AC18" s="240" t="n"/>
+      <c r="AD18" s="240" t="n"/>
+      <c r="AE18" s="240" t="n"/>
+      <c r="AF18" s="240" t="n"/>
+      <c r="AG18" s="240" t="n"/>
+      <c r="AH18" s="240" t="n"/>
+      <c r="AI18" s="240" t="n"/>
+      <c r="AJ18" s="240" t="n"/>
+      <c r="AK18" s="240" t="n"/>
+      <c r="AL18" s="240" t="n"/>
+      <c r="AM18" s="241">
         <f>IF($A17="","",IF(OR($N17="Yes",$S17="Yes",$X17="Yes",$AC17="Yes",$AH17="Yes"),"Yes","No"))</f>
         <v/>
       </c>
-      <c r="AN17" s="241">
+      <c r="AN18" s="241">
         <f>IF($A17="","",IFERROR(IF($AI17&lt;&gt;"",$AI17,IF($AD17&lt;&gt;"",$AD17,IF($Y17&lt;&gt;"",$Y17,IF($T17&lt;&gt;"",$T17,IF($O17&lt;&gt;"",$O17,""))))),""))</f>
         <v/>
       </c>
-      <c r="AO17" s="241">
+      <c r="AO18" s="241">
         <f>IFERROR(IF($AJ17&lt;&gt;"",$AJ17,IF($AE17&lt;&gt;"",$AE17,IF($Z17&lt;&gt;"",$Z17,IF($U17&lt;&gt;"",$U17,IF($P17&lt;&gt;"",$P17,""))))),"")</f>
         <v/>
       </c>
-      <c r="AP17" s="240" t="inlineStr">
+      <c r="AP18" s="240" t="inlineStr">
         <is>
           <t>Technique: EP-crown</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="60" customHeight="1" s="206">
-      <c r="A18" s="245">
-        <f>IF(C18="","",$C$2&amp;"."&amp;COUNTA($C$8:C18)&amp;"")</f>
+    <row r="19" ht="60" customHeight="1" s="206">
+      <c r="A19" s="245">
+        <f>IF(C19="","",$C$2&amp;"."&amp;COUNTA($C$8:C19)&amp;"")</f>
         <v/>
       </c>
-      <c r="B18" s="244" t="inlineStr">
+      <c r="B19" s="244" t="inlineStr">
         <is>
           <t>REQ-GIFT-001</t>
         </is>
       </c>
-      <c r="C18" s="244" t="inlineStr">
+      <c r="C19" s="244" t="inlineStr">
         <is>
           <t>DOC-v1.0-01 §D3/§D4 (GIFT-01, BR-GIFT-01) + DOC-v1.0-02 §3.8 + ảnh DOC-v1.0-04</t>
         </is>
       </c>
-      <c r="D18" s="244" t="inlineStr">
+      <c r="D19" s="244" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="E18" s="244" t="inlineStr">
+      <c r="E19" s="244" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F18" s="244" t="inlineStr">
+      <c r="F19" s="244" t="inlineStr">
         <is>
           <t>Check chỉ chọn được 1 loại quà tại một thời điểm (chọn loại khác thì bỏ loại cũ)</t>
         </is>
       </c>
-      <c r="G18" s="244" t="inlineStr">
+      <c r="G19" s="244" t="inlineStr">
         <is>
           <t>Đang ở màn Tặng quà, đã chọn sẵn chip "🌷 Bông hoa"</t>
         </is>
       </c>
-      <c r="H18" s="244" t="inlineStr">
+      <c r="H19" s="244" t="inlineStr">
         <is>
           <t>1. Mở app FoxEco bằng tài khoản Người gửi (Sender)
 2. Bấm tab "Hoạt động", mở đơn đã "Hoàn thành" để vào màn "Theo dõi đơn", bấm "✓ Cảm ơn người vận chuyển"
 3. Bấm chip "🌷 Bông hoa", sau đó bấm tiếp chip "👑 Vương miện"</t>
         </is>
       </c>
-      <c r="I18" s="244" t="inlineStr">
+      <c r="I19" s="244" t="inlineStr">
         <is>
           <t>3. Chỉ chip "👑 Vương miện" ở trạng thái đã chọn; chip "🌷 Bông hoa" trở về trạng thái chưa chọn — không cho chọn đồng thời 2 loại</t>
         </is>
       </c>
-      <c r="J18" s="246" t="inlineStr">
+      <c r="J19" s="246" t="inlineStr">
         <is>
           <t>AI</t>
         </is>
       </c>
-      <c r="K18" s="246" t="inlineStr">
+      <c r="K19" s="246" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="L18" s="246" t="inlineStr">
+      <c r="L19" s="246" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="M18" s="246" t="n"/>
-      <c r="N18" s="246" t="n"/>
-      <c r="O18" s="246" t="n"/>
-      <c r="P18" s="246" t="n"/>
-      <c r="Q18" s="246" t="n"/>
-      <c r="R18" s="246" t="n"/>
-      <c r="S18" s="246" t="n"/>
-      <c r="T18" s="246" t="n"/>
-      <c r="U18" s="246" t="n"/>
-      <c r="V18" s="246" t="n"/>
-      <c r="W18" s="246" t="n"/>
-      <c r="X18" s="246" t="n"/>
-      <c r="Y18" s="246" t="n"/>
-      <c r="Z18" s="246" t="n"/>
-      <c r="AA18" s="246" t="n"/>
-      <c r="AB18" s="247" t="n"/>
-      <c r="AC18" s="247" t="n"/>
-      <c r="AD18" s="247" t="n"/>
-      <c r="AE18" s="247" t="n"/>
-      <c r="AF18" s="247" t="n"/>
-      <c r="AG18" s="247" t="n"/>
-      <c r="AH18" s="247" t="n"/>
-      <c r="AI18" s="247" t="n"/>
-      <c r="AJ18" s="247" t="n"/>
-      <c r="AK18" s="247" t="n"/>
-      <c r="AL18" s="247" t="n"/>
-      <c r="AM18" s="248">
+      <c r="M19" s="246" t="n"/>
+      <c r="N19" s="246" t="n"/>
+      <c r="O19" s="246" t="n"/>
+      <c r="P19" s="246" t="n"/>
+      <c r="Q19" s="246" t="n"/>
+      <c r="R19" s="246" t="n"/>
+      <c r="S19" s="246" t="n"/>
+      <c r="T19" s="246" t="n"/>
+      <c r="U19" s="246" t="n"/>
+      <c r="V19" s="246" t="n"/>
+      <c r="W19" s="246" t="n"/>
+      <c r="X19" s="246" t="n"/>
+      <c r="Y19" s="246" t="n"/>
+      <c r="Z19" s="246" t="n"/>
+      <c r="AA19" s="246" t="n"/>
+      <c r="AB19" s="247" t="n"/>
+      <c r="AC19" s="247" t="n"/>
+      <c r="AD19" s="247" t="n"/>
+      <c r="AE19" s="247" t="n"/>
+      <c r="AF19" s="247" t="n"/>
+      <c r="AG19" s="247" t="n"/>
+      <c r="AH19" s="247" t="n"/>
+      <c r="AI19" s="247" t="n"/>
+      <c r="AJ19" s="247" t="n"/>
+      <c r="AK19" s="247" t="n"/>
+      <c r="AL19" s="247" t="n"/>
+      <c r="AM19" s="248">
         <f>IF($A18="","",IF(OR($N18="Yes",$S18="Yes",$X18="Yes",$AC18="Yes",$AH18="Yes"),"Yes","No"))</f>
         <v/>
       </c>
-      <c r="AN18" s="248">
+      <c r="AN19" s="248">
         <f>IF($A18="","",IFERROR(IF($AI18&lt;&gt;"",$AI18,IF($AD18&lt;&gt;"",$AD18,IF($Y18&lt;&gt;"",$Y18,IF($T18&lt;&gt;"",$T18,IF($O18&lt;&gt;"",$O18,""))))),""))</f>
         <v/>
       </c>
-      <c r="AO18" s="248">
+      <c r="AO19" s="248">
         <f>IFERROR(IF($AJ18&lt;&gt;"",$AJ18,IF($AE18&lt;&gt;"",$AE18,IF($Z18&lt;&gt;"",$Z18,IF($U18&lt;&gt;"",$U18,IF($P18&lt;&gt;"",$P18,""))))),"")</f>
         <v/>
       </c>
-      <c r="AP18" s="248" t="inlineStr">
+      <c r="AP19" s="248" t="inlineStr">
         <is>
           <t>Technique: EP-switch-selection (rule chọn 1 trong 4, nguồn: "Chọn 1 (chip có viền cam khi selected)" — DOC-v1.0-02 §3.8)</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="60" customHeight="1" s="206">
-      <c r="A19" s="239">
-        <f>IF(C19="","",$C$2&amp;"."&amp;COUNTA($C$8:C19)&amp;"")</f>
+    <row r="20" ht="60" customHeight="1" s="206">
+      <c r="A20" s="239">
+        <f>IF(C20="","",$C$2&amp;"."&amp;COUNTA($C$8:C20)&amp;"")</f>
         <v/>
       </c>
-      <c r="B19" s="239" t="inlineStr">
+      <c r="B20" s="239" t="inlineStr">
         <is>
           <t>REQ-GIFT-001</t>
         </is>
       </c>
-      <c r="C19" s="239" t="inlineStr">
+      <c r="C20" s="239" t="inlineStr">
         <is>
           <t>DOC-v1.0-01 §D3/§D4 (GIFT-01, BR-GIFT-01) + DOC-v1.0-02 §3.8 + ảnh DOC-v1.0-04</t>
         </is>
       </c>
-      <c r="D19" s="239" t="inlineStr">
+      <c r="D20" s="239" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="E19" s="239" t="inlineStr">
+      <c r="E20" s="239" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F19" s="239" t="inlineStr">
+      <c r="F20" s="239" t="inlineStr">
         <is>
           <t>Check bấm "Xác nhận tặng quà" khi chưa chọn loại quà nào</t>
         </is>
       </c>
-      <c r="G19" s="239" t="inlineStr">
+      <c r="G20" s="239" t="inlineStr">
         <is>
           <t>Đang ở màn Tặng quà, CHƯA chọn loại quà nào</t>
         </is>
       </c>
-      <c r="H19" s="239" t="inlineStr">
+      <c r="H20" s="239" t="inlineStr">
         <is>
           <t>1. Mở app FoxEco bằng tài khoản Người gửi (Sender)
 2. Bấm tab "Hoạt động", mở đơn đã "Hoàn thành" để vào màn "Theo dõi đơn", bấm "✓ Cảm ơn người vận chuyển"
 3. Bấm thẳng nút "✓ Xác nhận tặng quà" mà không chọn chip nào</t>
         </is>
       </c>
-      <c r="I19" s="239" t="inlineStr">
+      <c r="I20" s="239" t="inlineStr">
         <is>
           <t>3. Hệ thống KHÔNG gửi đi món quà nào — hoặc nút ở trạng thái disable không phản hồi, hoặc hiện thông báo yêu cầu chọn quà; tuyệt đối KHÔNG gửi quà rỗng hay tự chọn giúp 1 loại mặc định</t>
         </is>
       </c>
-      <c r="J19" s="239" t="inlineStr">
+      <c r="J20" s="239" t="inlineStr">
         <is>
           <t>AI</t>
         </is>
       </c>
-      <c r="K19" s="239" t="inlineStr">
+      <c r="K20" s="239" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="L19" s="239" t="inlineStr">
+      <c r="L20" s="239" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="M19" s="239" t="n"/>
-      <c r="N19" s="239" t="n"/>
-      <c r="O19" s="239" t="n"/>
-      <c r="P19" s="239" t="n"/>
-      <c r="Q19" s="239" t="n"/>
-      <c r="R19" s="239" t="n"/>
-      <c r="S19" s="239" t="n"/>
-      <c r="T19" s="239" t="n"/>
-      <c r="U19" s="239" t="n"/>
-      <c r="V19" s="239" t="n"/>
-      <c r="W19" s="239" t="n"/>
-      <c r="X19" s="239" t="n"/>
-      <c r="Y19" s="239" t="n"/>
-      <c r="Z19" s="239" t="n"/>
-      <c r="AA19" s="239" t="n"/>
-      <c r="AB19" s="240" t="n"/>
-      <c r="AC19" s="240" t="n"/>
-      <c r="AD19" s="240" t="n"/>
-      <c r="AE19" s="240" t="n"/>
-      <c r="AF19" s="240" t="n"/>
-      <c r="AG19" s="240" t="n"/>
-      <c r="AH19" s="240" t="n"/>
-      <c r="AI19" s="240" t="n"/>
-      <c r="AJ19" s="240" t="n"/>
-      <c r="AK19" s="240" t="n"/>
-      <c r="AL19" s="240" t="n"/>
-      <c r="AM19" s="241">
+      <c r="M20" s="239" t="n"/>
+      <c r="N20" s="239" t="n"/>
+      <c r="O20" s="239" t="n"/>
+      <c r="P20" s="239" t="n"/>
+      <c r="Q20" s="239" t="n"/>
+      <c r="R20" s="239" t="n"/>
+      <c r="S20" s="239" t="n"/>
+      <c r="T20" s="239" t="n"/>
+      <c r="U20" s="239" t="n"/>
+      <c r="V20" s="239" t="n"/>
+      <c r="W20" s="239" t="n"/>
+      <c r="X20" s="239" t="n"/>
+      <c r="Y20" s="239" t="n"/>
+      <c r="Z20" s="239" t="n"/>
+      <c r="AA20" s="239" t="n"/>
+      <c r="AB20" s="240" t="n"/>
+      <c r="AC20" s="240" t="n"/>
+      <c r="AD20" s="240" t="n"/>
+      <c r="AE20" s="240" t="n"/>
+      <c r="AF20" s="240" t="n"/>
+      <c r="AG20" s="240" t="n"/>
+      <c r="AH20" s="240" t="n"/>
+      <c r="AI20" s="240" t="n"/>
+      <c r="AJ20" s="240" t="n"/>
+      <c r="AK20" s="240" t="n"/>
+      <c r="AL20" s="240" t="n"/>
+      <c r="AM20" s="241">
         <f>IF($A19="","",IF(OR($N19="Yes",$S19="Yes",$X19="Yes",$AC19="Yes",$AH19="Yes"),"Yes","No"))</f>
         <v/>
       </c>
-      <c r="AN19" s="241">
+      <c r="AN20" s="241">
         <f>IF($A19="","",IFERROR(IF($AI19&lt;&gt;"",$AI19,IF($AD19&lt;&gt;"",$AD19,IF($Y19&lt;&gt;"",$Y19,IF($T19&lt;&gt;"",$T19,IF($O19&lt;&gt;"",$O19,""))))),""))</f>
         <v/>
       </c>
-      <c r="AO19" s="241">
+      <c r="AO20" s="241">
         <f>IFERROR(IF($AJ19&lt;&gt;"",$AJ19,IF($AE19&lt;&gt;"",$AE19,IF($Z19&lt;&gt;"",$Z19,IF($U19&lt;&gt;"",$U19,IF($P19&lt;&gt;"",$P19,""))))),"")</f>
         <v/>
       </c>
-      <c r="AP19" s="240" t="inlineStr">
+      <c r="AP20" s="240" t="inlineStr">
         <is>
           <t>Technique: EP-invalid-none | ⚠ `test_data_catalog.md` ghi rõ rule validate cho case này CHƯA có trong tài liệu ("chưa có rule validate rõ — suy đoán phải chọn 1 mới gửi được") → Expected cố ý viết ở mức bất biến an toàn (không gửi quà rỗng), chấp nhận cả 2 cách hiện thực. **Cần BA chốt** hành vi chính thức để siết Expected lại (Project_rule.md §10.1)</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="20" customHeight="1" s="206">
-      <c r="A20" s="231" t="n"/>
-      <c r="B20" s="232" t="inlineStr">
+    <row r="21" ht="20" customHeight="1" s="206">
+      <c r="A21" s="231" t="n"/>
+      <c r="B21" s="232" t="inlineStr">
         <is>
           <t>Block Gửi quà &amp; popup kết quả</t>
         </is>
       </c>
-      <c r="C20" s="233" t="n"/>
-      <c r="D20" s="233" t="n"/>
-      <c r="E20" s="233" t="n"/>
-      <c r="F20" s="233" t="n"/>
-      <c r="G20" s="233" t="n"/>
-      <c r="H20" s="233" t="n"/>
-      <c r="I20" s="234" t="n"/>
-      <c r="J20" s="231" t="n"/>
-      <c r="K20" s="231" t="n"/>
-      <c r="L20" s="231" t="n"/>
-      <c r="M20" s="231" t="n"/>
-      <c r="N20" s="235" t="n"/>
-      <c r="O20" s="235" t="n"/>
-      <c r="P20" s="235" t="n"/>
-      <c r="Q20" s="235" t="n"/>
-      <c r="R20" s="235" t="n"/>
-      <c r="S20" s="235" t="n"/>
-      <c r="T20" s="235" t="n"/>
-      <c r="U20" s="235" t="n"/>
-      <c r="V20" s="235" t="n"/>
-      <c r="W20" s="235" t="n"/>
-      <c r="X20" s="235" t="n"/>
-      <c r="Y20" s="235" t="n"/>
-      <c r="Z20" s="235" t="n"/>
-      <c r="AA20" s="235" t="n"/>
-      <c r="AB20" s="236" t="n"/>
-      <c r="AC20" s="236" t="n"/>
-      <c r="AD20" s="236" t="n"/>
-      <c r="AE20" s="236" t="n"/>
-      <c r="AF20" s="236" t="n"/>
-      <c r="AG20" s="236" t="n"/>
-      <c r="AH20" s="236" t="n"/>
-      <c r="AI20" s="236" t="n"/>
-      <c r="AJ20" s="236" t="n"/>
-      <c r="AK20" s="236" t="n"/>
-      <c r="AL20" s="236" t="n"/>
-      <c r="AM20" s="237" t="n"/>
-      <c r="AN20" s="237" t="n"/>
-      <c r="AO20" s="237" t="n"/>
-      <c r="AP20" s="238" t="n"/>
-    </row>
-    <row r="21" ht="60" customHeight="1" s="206">
-      <c r="A21" s="239">
-        <f>IF(C21="","",$C$2&amp;"."&amp;COUNTA($C$8:C21)&amp;"")</f>
-        <v/>
-      </c>
-      <c r="B21" s="243" t="inlineStr">
-        <is>
-          <t>REQ-GIFT-001</t>
-        </is>
-      </c>
-      <c r="C21" s="244" t="inlineStr">
-        <is>
-          <t>DOC-v1.0-01 §D3/§D4 (GIFT-01, BR-GIFT-01) + DOC-v1.0-02 §3.8 + ảnh DOC-v1.0-04</t>
-        </is>
-      </c>
-      <c r="D21" s="244" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="E21" s="244" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F21" s="244" t="inlineStr">
-        <is>
-          <t>Check gửi quà thành công hiện ngay popup kết quả, không cần Người vận chuyển xác nhận</t>
-        </is>
-      </c>
-      <c r="G21" s="244" t="inlineStr">
-        <is>
-          <t>Đang ở màn Tặng quà, đã chọn chip "☕ Ly cà phê"</t>
-        </is>
-      </c>
-      <c r="H21" s="244" t="inlineStr">
-        <is>
-          <t>1. Mở app FoxEco bằng tài khoản Người gửi (Sender)
-2. Bấm tab "Hoạt động", mở đơn đã "Hoàn thành" để vào màn "Theo dõi đơn", bấm "✓ Cảm ơn người vận chuyển"
-3. Bấm chip "☕ Ly cà phê" rồi bấm "✓ Xác nhận tặng quà"</t>
-        </is>
-      </c>
-      <c r="I21" s="244" t="inlineStr">
-        <is>
-          <t>3. Popup kết quả hiện NGAY lập tức — không phát sinh bước chờ Người vận chuyển chấp nhận/xác nhận</t>
-        </is>
-      </c>
-      <c r="J21" s="239" t="inlineStr">
-        <is>
-          <t>AI</t>
-        </is>
-      </c>
-      <c r="K21" s="239" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="L21" s="239" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M21" s="239" t="n"/>
-      <c r="N21" s="239" t="n"/>
-      <c r="O21" s="239" t="n"/>
-      <c r="P21" s="239" t="n"/>
-      <c r="Q21" s="239" t="n"/>
-      <c r="R21" s="239" t="n"/>
-      <c r="S21" s="239" t="n"/>
-      <c r="T21" s="239" t="n"/>
-      <c r="U21" s="239" t="n"/>
-      <c r="V21" s="239" t="n"/>
-      <c r="W21" s="239" t="n"/>
-      <c r="X21" s="239" t="n"/>
-      <c r="Y21" s="239" t="n"/>
-      <c r="Z21" s="239" t="n"/>
-      <c r="AA21" s="239" t="n"/>
-      <c r="AB21" s="240" t="n"/>
-      <c r="AC21" s="240" t="n"/>
-      <c r="AD21" s="240" t="n"/>
-      <c r="AE21" s="240" t="n"/>
-      <c r="AF21" s="240" t="n"/>
-      <c r="AG21" s="240" t="n"/>
-      <c r="AH21" s="240" t="n"/>
-      <c r="AI21" s="240" t="n"/>
-      <c r="AJ21" s="240" t="n"/>
-      <c r="AK21" s="240" t="n"/>
-      <c r="AL21" s="240" t="n"/>
-      <c r="AM21" s="241">
-        <f>IF($A21="","",IF(OR($N21="Yes",$S21="Yes",$X21="Yes",$AC21="Yes",$AH21="Yes"),"Yes","No"))</f>
-        <v/>
-      </c>
-      <c r="AN21" s="241">
-        <f>IF($A21="","",IFERROR(IF($AI21&lt;&gt;"",$AI21,IF($AD21&lt;&gt;"",$AD21,IF($Y21&lt;&gt;"",$Y21,IF($T21&lt;&gt;"",$T21,IF($O21&lt;&gt;"",$O21,""))))),""))</f>
-        <v/>
-      </c>
-      <c r="AO21" s="241">
-        <f>IFERROR(IF($AJ21&lt;&gt;"",$AJ21,IF($AE21&lt;&gt;"",$AE21,IF($Z21&lt;&gt;"",$Z21,IF($U21&lt;&gt;"",$U21,IF($P21&lt;&gt;"",$P21,""))))),"")</f>
-        <v/>
-      </c>
-      <c r="AP21" s="240" t="n"/>
+      <c r="C21" s="211" t="n"/>
+      <c r="D21" s="211" t="n"/>
+      <c r="E21" s="211" t="n"/>
+      <c r="F21" s="211" t="n"/>
+      <c r="G21" s="211" t="n"/>
+      <c r="H21" s="211" t="n"/>
+      <c r="I21" s="209" t="n"/>
+      <c r="J21" s="231" t="n"/>
+      <c r="K21" s="231" t="n"/>
+      <c r="L21" s="231" t="n"/>
+      <c r="M21" s="231" t="n"/>
+      <c r="N21" s="235" t="n"/>
+      <c r="O21" s="235" t="n"/>
+      <c r="P21" s="235" t="n"/>
+      <c r="Q21" s="235" t="n"/>
+      <c r="R21" s="235" t="n"/>
+      <c r="S21" s="235" t="n"/>
+      <c r="T21" s="235" t="n"/>
+      <c r="U21" s="235" t="n"/>
+      <c r="V21" s="235" t="n"/>
+      <c r="W21" s="235" t="n"/>
+      <c r="X21" s="235" t="n"/>
+      <c r="Y21" s="235" t="n"/>
+      <c r="Z21" s="235" t="n"/>
+      <c r="AA21" s="235" t="n"/>
+      <c r="AB21" s="236" t="n"/>
+      <c r="AC21" s="236" t="n"/>
+      <c r="AD21" s="236" t="n"/>
+      <c r="AE21" s="236" t="n"/>
+      <c r="AF21" s="236" t="n"/>
+      <c r="AG21" s="236" t="n"/>
+      <c r="AH21" s="236" t="n"/>
+      <c r="AI21" s="236" t="n"/>
+      <c r="AJ21" s="236" t="n"/>
+      <c r="AK21" s="236" t="n"/>
+      <c r="AL21" s="236" t="n"/>
+      <c r="AM21" s="237" t="n"/>
+      <c r="AN21" s="237" t="n"/>
+      <c r="AO21" s="237" t="n"/>
+      <c r="AP21" s="238" t="n"/>
     </row>
     <row r="22" ht="60" customHeight="1" s="206">
       <c r="A22" s="239">
         <f>IF(C22="","",$C$2&amp;"."&amp;COUNTA($C$8:C22)&amp;"")</f>
         <v/>
       </c>
-      <c r="B22" s="239" t="inlineStr">
+      <c r="B22" s="243" t="inlineStr">
         <is>
           <t>REQ-GIFT-001</t>
         </is>
       </c>
-      <c r="C22" s="239" t="inlineStr">
+      <c r="C22" s="244" t="inlineStr">
         <is>
           <t>DOC-v1.0-01 §D3/§D4 (GIFT-01, BR-GIFT-01) + DOC-v1.0-02 §3.8 + ảnh DOC-v1.0-04</t>
         </is>
       </c>
-      <c r="D22" s="239" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="E22" s="239" t="inlineStr">
+      <c r="D22" s="244" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E22" s="244" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F22" s="239" t="inlineStr">
-        <is>
-          <t>Check đầy đủ + đúng 3 thành phần hiển thị tại popup "Đã gửi lời cảm ơn!"</t>
-        </is>
-      </c>
-      <c r="G22" s="239" t="inlineStr">
-        <is>
-          <t>Sender vừa bấm "✓ Xác nhận tặng quà" với 1 loại quà đã chọn</t>
-        </is>
-      </c>
-      <c r="H22" s="239" t="inlineStr">
+      <c r="F22" s="244" t="inlineStr">
+        <is>
+          <t>Check gửi quà thành công hiện ngay popup kết quả, không cần Người vận chuyển xác nhận</t>
+        </is>
+      </c>
+      <c r="G22" s="244" t="inlineStr">
+        <is>
+          <t>Đang ở màn Tặng quà, đã chọn chip "☕ Ly cà phê"</t>
+        </is>
+      </c>
+      <c r="H22" s="244" t="inlineStr">
         <is>
           <t>1. Mở app FoxEco bằng tài khoản Người gửi (Sender)
 2. Bấm tab "Hoạt động", mở đơn đã "Hoàn thành" để vào màn "Theo dõi đơn", bấm "✓ Cảm ơn người vận chuyển"
-3. Chọn 1 loại quà, bấm "✓ Xác nhận tặng quà" và quan sát popup kết quả</t>
-        </is>
-      </c>
-      <c r="I22" s="239" t="inlineStr">
-        <is>
-          <t>3. Popup hiển thị đủ 3 thành phần: (1) title "Đã gửi lời cảm ơn!", (2) nội dung "Món quà và lời cảm ơn của bạn đã được gửi đến người vận chuyển.", (3) nút "Về trang chủ"</t>
+3. Bấm chip "☕ Ly cà phê" rồi bấm "✓ Xác nhận tặng quà"</t>
+        </is>
+      </c>
+      <c r="I22" s="244" t="inlineStr">
+        <is>
+          <t>3. Popup kết quả hiện NGAY lập tức — không phát sinh bước chờ Người vận chuyển chấp nhận/xác nhận</t>
         </is>
       </c>
       <c r="J22" s="239" t="inlineStr">
@@ -4020,22 +4025,18 @@
       <c r="AK22" s="240" t="n"/>
       <c r="AL22" s="240" t="n"/>
       <c r="AM22" s="241">
-        <f>IF($A22="","",IF(OR($N22="Yes",$S22="Yes",$X22="Yes",$AC22="Yes",$AH22="Yes"),"Yes","No"))</f>
+        <f>IF($A21="","",IF(OR($N21="Yes",$S21="Yes",$X21="Yes",$AC21="Yes",$AH21="Yes"),"Yes","No"))</f>
         <v/>
       </c>
       <c r="AN22" s="241">
-        <f>IF($A22="","",IFERROR(IF($AI22&lt;&gt;"",$AI22,IF($AD22&lt;&gt;"",$AD22,IF($Y22&lt;&gt;"",$Y22,IF($T22&lt;&gt;"",$T22,IF($O22&lt;&gt;"",$O22,""))))),""))</f>
+        <f>IF($A21="","",IFERROR(IF($AI21&lt;&gt;"",$AI21,IF($AD21&lt;&gt;"",$AD21,IF($Y21&lt;&gt;"",$Y21,IF($T21&lt;&gt;"",$T21,IF($O21&lt;&gt;"",$O21,""))))),""))</f>
         <v/>
       </c>
       <c r="AO22" s="241">
-        <f>IFERROR(IF($AJ22&lt;&gt;"",$AJ22,IF($AE22&lt;&gt;"",$AE22,IF($Z22&lt;&gt;"",$Z22,IF($U22&lt;&gt;"",$U22,IF($P22&lt;&gt;"",$P22,""))))),"")</f>
+        <f>IFERROR(IF($AJ21&lt;&gt;"",$AJ21,IF($AE21&lt;&gt;"",$AE21,IF($Z21&lt;&gt;"",$Z21,IF($U21&lt;&gt;"",$U21,IF($P21&lt;&gt;"",$P21,""))))),"")</f>
         <v/>
       </c>
-      <c r="AP22" s="240" t="inlineStr">
-        <is>
-          <t>Field/column completeness check — auto-derived (xem generate.md Step 3b) | Text verbatim xác nhận qua ảnh Figma DOC-v1.0-04 (hash 808c2576…, 851d2b9f…)</t>
-        </is>
-      </c>
+      <c r="AP22" s="240" t="n"/>
     </row>
     <row r="23" ht="60" customHeight="1" s="206">
       <c r="A23" s="239">
@@ -4054,34 +4055,34 @@
       </c>
       <c r="D23" s="239" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="E23" s="239" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F23" s="239" t="inlineStr">
         <is>
-          <t>Check bấm "Về trang chủ" trong popup kết quả điều hướng đúng Trang chủ</t>
+          <t>Check đầy đủ + đúng 3 thành phần hiển thị tại popup "Đã gửi lời cảm ơn!"</t>
         </is>
       </c>
       <c r="G23" s="239" t="inlineStr">
         <is>
-          <t>Popup "Đã gửi lời cảm ơn!" đang hiển thị sau khi gửi quà thành công</t>
+          <t>Sender vừa bấm "✓ Xác nhận tặng quà" với 1 loại quà đã chọn</t>
         </is>
       </c>
       <c r="H23" s="239" t="inlineStr">
         <is>
           <t>1. Mở app FoxEco bằng tài khoản Người gửi (Sender)
 2. Bấm tab "Hoạt động", mở đơn đã "Hoàn thành" để vào màn "Theo dõi đơn", bấm "✓ Cảm ơn người vận chuyển"
-3. Chọn 1 loại quà, bấm "✓ Xác nhận tặng quà", sau đó bấm nút "Về trang chủ" trong popup</t>
+3. Chọn 1 loại quà, bấm "✓ Xác nhận tặng quà" và quan sát popup kết quả</t>
         </is>
       </c>
       <c r="I23" s="239" t="inlineStr">
         <is>
-          <t>3. Popup đóng lại và điều hướng về đúng màn Trang chủ (tab "Trang chủ" tại bottom nav được highlight)</t>
+          <t>3. Popup hiển thị đủ 3 thành phần: (1) title "Đã gửi lời cảm ơn!", (2) nội dung "Món quà và lời cảm ơn của bạn đã được gửi đến người vận chuyển.", (3) nút "Về trang chủ"</t>
         </is>
       </c>
       <c r="J23" s="239" t="inlineStr">
@@ -4126,18 +4127,22 @@
       <c r="AK23" s="240" t="n"/>
       <c r="AL23" s="240" t="n"/>
       <c r="AM23" s="241">
-        <f>IF($A23="","",IF(OR($N23="Yes",$S23="Yes",$X23="Yes",$AC23="Yes",$AH23="Yes"),"Yes","No"))</f>
+        <f>IF($A22="","",IF(OR($N22="Yes",$S22="Yes",$X22="Yes",$AC22="Yes",$AH22="Yes"),"Yes","No"))</f>
         <v/>
       </c>
       <c r="AN23" s="241">
-        <f>IF($A23="","",IFERROR(IF($AI23&lt;&gt;"",$AI23,IF($AD23&lt;&gt;"",$AD23,IF($Y23&lt;&gt;"",$Y23,IF($T23&lt;&gt;"",$T23,IF($O23&lt;&gt;"",$O23,""))))),""))</f>
+        <f>IF($A22="","",IFERROR(IF($AI22&lt;&gt;"",$AI22,IF($AD22&lt;&gt;"",$AD22,IF($Y22&lt;&gt;"",$Y22,IF($T22&lt;&gt;"",$T22,IF($O22&lt;&gt;"",$O22,""))))),""))</f>
         <v/>
       </c>
       <c r="AO23" s="241">
-        <f>IFERROR(IF($AJ23&lt;&gt;"",$AJ23,IF($AE23&lt;&gt;"",$AE23,IF($Z23&lt;&gt;"",$Z23,IF($U23&lt;&gt;"",$U23,IF($P23&lt;&gt;"",$P23,""))))),"")</f>
+        <f>IFERROR(IF($AJ22&lt;&gt;"",$AJ22,IF($AE22&lt;&gt;"",$AE22,IF($Z22&lt;&gt;"",$Z22,IF($U22&lt;&gt;"",$U22,IF($P22&lt;&gt;"",$P22,""))))),"")</f>
         <v/>
       </c>
-      <c r="AP23" s="240" t="n"/>
+      <c r="AP23" s="240" t="inlineStr">
+        <is>
+          <t>Field/column completeness check — auto-derived (xem generate.md Step 3b) | Text verbatim xác nhận qua ảnh Figma DOC-v1.0-04 (hash 808c2576…, 851d2b9f…)</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="60" customHeight="1" s="206">
       <c r="A24" s="239">
@@ -4156,34 +4161,34 @@
       </c>
       <c r="D24" s="239" t="inlineStr">
         <is>
-          <t>Integration</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="E24" s="239" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="F24" s="239" t="inlineStr">
         <is>
-          <t>Check "Quà đã nhận" của Người vận chuyển tăng đúng loại quà vừa được tặng</t>
+          <t>Check bấm "Về trang chủ" trong popup kết quả điều hướng đúng Trang chủ</t>
         </is>
       </c>
       <c r="G24" s="239" t="inlineStr">
         <is>
-          <t>Carrier của đơn đã ghi nhận sẵn số lượng quà từng loại trước khi Sender tặng; Sender vừa gửi "☕ Ly cà phê" thành công</t>
+          <t>Popup "Đã gửi lời cảm ơn!" đang hiển thị sau khi gửi quà thành công</t>
         </is>
       </c>
       <c r="H24" s="239" t="inlineStr">
         <is>
-          <t>1. Ghi nhận số lượng "☕ Ly cà phê" hiện có tại màn "Quà đã nhận" của tài khoản Carrier
-2. Trên thiết bị Sender: gửi quà "☕ Ly cà phê" cho đơn đã hoàn thành của Carrier đó
-3. Mở lại màn "Quà đã nhận" của tài khoản Carrier (Cá nhân → "Quà đã nhận")</t>
+          <t>1. Mở app FoxEco bằng tài khoản Người gửi (Sender)
+2. Bấm tab "Hoạt động", mở đơn đã "Hoàn thành" để vào màn "Theo dõi đơn", bấm "✓ Cảm ơn người vận chuyển"
+3. Chọn 1 loại quà, bấm "✓ Xác nhận tặng quà", sau đó bấm nút "Về trang chủ" trong popup</t>
         </is>
       </c>
       <c r="I24" s="239" t="inlineStr">
         <is>
-          <t>3. Số lượng "☕ Ly cà phê" tăng đúng 1 so với bước 1; các loại quà khác giữ nguyên; Carrier KHÔNG phải thao tác xác nhận nào để nhận quà</t>
+          <t>3. Popup đóng lại và điều hướng về đúng màn Trang chủ (tab "Trang chủ" tại bottom nav được highlight)</t>
         </is>
       </c>
       <c r="J24" s="239" t="inlineStr">
@@ -4228,176 +4233,172 @@
       <c r="AK24" s="240" t="n"/>
       <c r="AL24" s="240" t="n"/>
       <c r="AM24" s="241">
+        <f>IF($A23="","",IF(OR($N23="Yes",$S23="Yes",$X23="Yes",$AC23="Yes",$AH23="Yes"),"Yes","No"))</f>
+        <v/>
+      </c>
+      <c r="AN24" s="241">
+        <f>IF($A23="","",IFERROR(IF($AI23&lt;&gt;"",$AI23,IF($AD23&lt;&gt;"",$AD23,IF($Y23&lt;&gt;"",$Y23,IF($T23&lt;&gt;"",$T23,IF($O23&lt;&gt;"",$O23,""))))),""))</f>
+        <v/>
+      </c>
+      <c r="AO24" s="241">
+        <f>IFERROR(IF($AJ23&lt;&gt;"",$AJ23,IF($AE23&lt;&gt;"",$AE23,IF($Z23&lt;&gt;"",$Z23,IF($U23&lt;&gt;"",$U23,IF($P23&lt;&gt;"",$P23,""))))),"")</f>
+        <v/>
+      </c>
+      <c r="AP24" s="240" t="n"/>
+    </row>
+    <row r="25" ht="60" customHeight="1" s="206">
+      <c r="A25" s="239">
+        <f>IF(C25="","",$C$2&amp;"."&amp;COUNTA($C$8:C25)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="B25" s="239" t="inlineStr">
+        <is>
+          <t>REQ-GIFT-001</t>
+        </is>
+      </c>
+      <c r="C25" s="239" t="inlineStr">
+        <is>
+          <t>DOC-v1.0-01 §D3/§D4 (GIFT-01, BR-GIFT-01) + DOC-v1.0-02 §3.8 + ảnh DOC-v1.0-04</t>
+        </is>
+      </c>
+      <c r="D25" s="239" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="E25" s="239" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F25" s="239" t="inlineStr">
+        <is>
+          <t>Check "Quà đã nhận" của Người vận chuyển tăng đúng loại quà vừa được tặng</t>
+        </is>
+      </c>
+      <c r="G25" s="239" t="inlineStr">
+        <is>
+          <t>Carrier của đơn đã ghi nhận sẵn số lượng quà từng loại trước khi Sender tặng; Sender vừa gửi "☕ Ly cà phê" thành công</t>
+        </is>
+      </c>
+      <c r="H25" s="239" t="inlineStr">
+        <is>
+          <t>1. Ghi nhận số lượng "☕ Ly cà phê" hiện có tại màn "Quà đã nhận" của tài khoản Carrier
+2. Trên thiết bị Sender: gửi quà "☕ Ly cà phê" cho đơn đã hoàn thành của Carrier đó
+3. Mở lại màn "Quà đã nhận" của tài khoản Carrier (Cá nhân → "Quà đã nhận")</t>
+        </is>
+      </c>
+      <c r="I25" s="239" t="inlineStr">
+        <is>
+          <t>3. Số lượng "☕ Ly cà phê" tăng đúng 1 so với bước 1; các loại quà khác giữ nguyên; Carrier KHÔNG phải thao tác xác nhận nào để nhận quà</t>
+        </is>
+      </c>
+      <c r="J25" s="239" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="K25" s="239" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="L25" s="239" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M25" s="239" t="n"/>
+      <c r="N25" s="239" t="n"/>
+      <c r="O25" s="239" t="n"/>
+      <c r="P25" s="239" t="n"/>
+      <c r="Q25" s="239" t="n"/>
+      <c r="R25" s="239" t="n"/>
+      <c r="S25" s="239" t="n"/>
+      <c r="T25" s="239" t="n"/>
+      <c r="U25" s="239" t="n"/>
+      <c r="V25" s="239" t="n"/>
+      <c r="W25" s="239" t="n"/>
+      <c r="X25" s="239" t="n"/>
+      <c r="Y25" s="239" t="n"/>
+      <c r="Z25" s="239" t="n"/>
+      <c r="AA25" s="239" t="n"/>
+      <c r="AB25" s="240" t="n"/>
+      <c r="AC25" s="240" t="n"/>
+      <c r="AD25" s="240" t="n"/>
+      <c r="AE25" s="240" t="n"/>
+      <c r="AF25" s="240" t="n"/>
+      <c r="AG25" s="240" t="n"/>
+      <c r="AH25" s="240" t="n"/>
+      <c r="AI25" s="240" t="n"/>
+      <c r="AJ25" s="240" t="n"/>
+      <c r="AK25" s="240" t="n"/>
+      <c r="AL25" s="240" t="n"/>
+      <c r="AM25" s="241">
         <f>IF($A24="","",IF(OR($N24="Yes",$S24="Yes",$X24="Yes",$AC24="Yes",$AH24="Yes"),"Yes","No"))</f>
         <v/>
       </c>
-      <c r="AN24" s="241">
+      <c r="AN25" s="241">
         <f>IF($A24="","",IFERROR(IF($AI24&lt;&gt;"",$AI24,IF($AD24&lt;&gt;"",$AD24,IF($Y24&lt;&gt;"",$Y24,IF($T24&lt;&gt;"",$T24,IF($O24&lt;&gt;"",$O24,""))))),""))</f>
         <v/>
       </c>
-      <c r="AO24" s="241">
+      <c r="AO25" s="241">
         <f>IFERROR(IF($AJ24&lt;&gt;"",$AJ24,IF($AE24&lt;&gt;"",$AE24,IF($Z24&lt;&gt;"",$Z24,IF($U24&lt;&gt;"",$U24,IF($P24&lt;&gt;"",$P24,""))))),"")</f>
         <v/>
       </c>
-      <c r="AP24" s="240" t="inlineStr">
+      <c r="AP25" s="240" t="inlineStr">
         <is>
           <t>Cấu trúc màn "Quà đã nhận" (card đếm theo loại + empty state + icon quay lại) đã cover tại TC-CANHAN (SC-GIFT-003/006/007) — tại đây chỉ verify tác động end-to-end của việc tặng quà</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="20" customHeight="1" s="206">
-      <c r="A25" s="231" t="n"/>
-      <c r="B25" s="242" t="inlineStr">
+    <row r="26" ht="20" customHeight="1" s="206">
+      <c r="A26" s="231" t="n"/>
+      <c r="B26" s="242" t="inlineStr">
         <is>
           <t>Block Đổi nhãn nút sau khi đã gửi quà</t>
         </is>
       </c>
-      <c r="C25" s="233" t="n"/>
-      <c r="D25" s="233" t="n"/>
-      <c r="E25" s="233" t="n"/>
-      <c r="F25" s="233" t="n"/>
-      <c r="G25" s="233" t="n"/>
-      <c r="H25" s="233" t="n"/>
-      <c r="I25" s="234" t="n"/>
-      <c r="J25" s="231" t="n"/>
-      <c r="K25" s="231" t="n"/>
-      <c r="L25" s="231" t="n"/>
-      <c r="M25" s="231" t="n"/>
-      <c r="N25" s="235" t="n"/>
-      <c r="O25" s="235" t="n"/>
-      <c r="P25" s="235" t="n"/>
-      <c r="Q25" s="235" t="n"/>
-      <c r="R25" s="235" t="n"/>
-      <c r="S25" s="235" t="n"/>
-      <c r="T25" s="235" t="n"/>
-      <c r="U25" s="235" t="n"/>
-      <c r="V25" s="235" t="n"/>
-      <c r="W25" s="235" t="n"/>
-      <c r="X25" s="235" t="n"/>
-      <c r="Y25" s="235" t="n"/>
-      <c r="Z25" s="235" t="n"/>
-      <c r="AA25" s="235" t="n"/>
-      <c r="AB25" s="236" t="n"/>
-      <c r="AC25" s="236" t="n"/>
-      <c r="AD25" s="236" t="n"/>
-      <c r="AE25" s="236" t="n"/>
-      <c r="AF25" s="236" t="n"/>
-      <c r="AG25" s="236" t="n"/>
-      <c r="AH25" s="236" t="n"/>
-      <c r="AI25" s="236" t="n"/>
-      <c r="AJ25" s="236" t="n"/>
-      <c r="AK25" s="236" t="n"/>
-      <c r="AL25" s="236" t="n"/>
-      <c r="AM25" s="237" t="n"/>
-      <c r="AN25" s="237" t="n"/>
-      <c r="AO25" s="237" t="n"/>
-      <c r="AP25" s="238" t="n"/>
-    </row>
-    <row r="26" ht="60" customHeight="1" s="206">
-      <c r="A26" s="239">
-        <f>IF(C26="","",$C$2&amp;"."&amp;COUNTA($C$8:C26)&amp;"")</f>
-        <v/>
-      </c>
-      <c r="B26" s="239" t="inlineStr">
-        <is>
-          <t>REQ-GIFT-003</t>
-        </is>
-      </c>
-      <c r="C26" s="239" t="inlineStr">
-        <is>
-          <t>Quan sát thực tế app STG + ảnh DOC-v1.0-04 (ma trận nhãn nút)</t>
-        </is>
-      </c>
-      <c r="D26" s="239" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="E26" s="239" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F26" s="239" t="inlineStr">
-        <is>
-          <t>Check nút "Cảm ơn người vận chuyển" đổi thành nhãn "Bạn đã đánh giá" sau khi gửi quà</t>
-        </is>
-      </c>
-      <c r="G26" s="239" t="inlineStr">
-        <is>
-          <t>Sender vừa gửi quà thành công cho 1 đơn đã "Hoàn thành"</t>
-        </is>
-      </c>
-      <c r="H26" s="239" t="inlineStr">
-        <is>
-          <t>1. Mở app FoxEco bằng tài khoản Sender, mở đơn đã "Hoàn thành" và gửi quà thành công
-2. Quay lại màn "Theo dõi đơn" của chính đơn vừa tặng quà
-3. Quan sát nút hành động ở đáy màn</t>
-        </is>
-      </c>
-      <c r="I26" s="239" t="inlineStr">
-        <is>
-          <t>3. Nút "✓ Cảm ơn người vận chuyển" đã đổi thành nhãn "Bạn đã đánh giá" ở trạng thái disable</t>
-        </is>
-      </c>
-      <c r="J26" s="239" t="inlineStr">
-        <is>
-          <t>AI</t>
-        </is>
-      </c>
-      <c r="K26" s="239" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="L26" s="239" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M26" s="239" t="n"/>
-      <c r="N26" s="239" t="n"/>
-      <c r="O26" s="239" t="n"/>
-      <c r="P26" s="239" t="n"/>
-      <c r="Q26" s="239" t="n"/>
-      <c r="R26" s="239" t="n"/>
-      <c r="S26" s="239" t="n"/>
-      <c r="T26" s="239" t="n"/>
-      <c r="U26" s="239" t="n"/>
-      <c r="V26" s="239" t="n"/>
-      <c r="W26" s="239" t="n"/>
-      <c r="X26" s="239" t="n"/>
-      <c r="Y26" s="239" t="n"/>
-      <c r="Z26" s="239" t="n"/>
-      <c r="AA26" s="239" t="n"/>
-      <c r="AB26" s="240" t="n"/>
-      <c r="AC26" s="240" t="n"/>
-      <c r="AD26" s="240" t="n"/>
-      <c r="AE26" s="240" t="n"/>
-      <c r="AF26" s="240" t="n"/>
-      <c r="AG26" s="240" t="n"/>
-      <c r="AH26" s="240" t="n"/>
-      <c r="AI26" s="240" t="n"/>
-      <c r="AJ26" s="240" t="n"/>
-      <c r="AK26" s="240" t="n"/>
-      <c r="AL26" s="240" t="n"/>
-      <c r="AM26" s="241">
-        <f>IF($A26="","",IF(OR($N26="Yes",$S26="Yes",$X26="Yes",$AC26="Yes",$AH26="Yes"),"Yes","No"))</f>
-        <v/>
-      </c>
-      <c r="AN26" s="241">
-        <f>IF($A26="","",IFERROR(IF($AI26&lt;&gt;"",$AI26,IF($AD26&lt;&gt;"",$AD26,IF($Y26&lt;&gt;"",$Y26,IF($T26&lt;&gt;"",$T26,IF($O26&lt;&gt;"",$O26,""))))),""))</f>
-        <v/>
-      </c>
-      <c r="AO26" s="241">
-        <f>IFERROR(IF($AJ26&lt;&gt;"",$AJ26,IF($AE26&lt;&gt;"",$AE26,IF($Z26&lt;&gt;"",$Z26,IF($U26&lt;&gt;"",$U26,IF($P26&lt;&gt;"",$P26,""))))),"")</f>
-        <v/>
-      </c>
-      <c r="AP26" s="240" t="inlineStr">
-        <is>
-          <t>Technique: ST-gift-not-sent → gift-sent (đổi trạng thái nút sau hành động gửi quà)</t>
-        </is>
-      </c>
+      <c r="C26" s="211" t="n"/>
+      <c r="D26" s="211" t="n"/>
+      <c r="E26" s="211" t="n"/>
+      <c r="F26" s="211" t="n"/>
+      <c r="G26" s="211" t="n"/>
+      <c r="H26" s="211" t="n"/>
+      <c r="I26" s="209" t="n"/>
+      <c r="J26" s="231" t="n"/>
+      <c r="K26" s="231" t="n"/>
+      <c r="L26" s="231" t="n"/>
+      <c r="M26" s="231" t="n"/>
+      <c r="N26" s="235" t="n"/>
+      <c r="O26" s="235" t="n"/>
+      <c r="P26" s="235" t="n"/>
+      <c r="Q26" s="235" t="n"/>
+      <c r="R26" s="235" t="n"/>
+      <c r="S26" s="235" t="n"/>
+      <c r="T26" s="235" t="n"/>
+      <c r="U26" s="235" t="n"/>
+      <c r="V26" s="235" t="n"/>
+      <c r="W26" s="235" t="n"/>
+      <c r="X26" s="235" t="n"/>
+      <c r="Y26" s="235" t="n"/>
+      <c r="Z26" s="235" t="n"/>
+      <c r="AA26" s="235" t="n"/>
+      <c r="AB26" s="236" t="n"/>
+      <c r="AC26" s="236" t="n"/>
+      <c r="AD26" s="236" t="n"/>
+      <c r="AE26" s="236" t="n"/>
+      <c r="AF26" s="236" t="n"/>
+      <c r="AG26" s="236" t="n"/>
+      <c r="AH26" s="236" t="n"/>
+      <c r="AI26" s="236" t="n"/>
+      <c r="AJ26" s="236" t="n"/>
+      <c r="AK26" s="236" t="n"/>
+      <c r="AL26" s="236" t="n"/>
+      <c r="AM26" s="237" t="n"/>
+      <c r="AN26" s="237" t="n"/>
+      <c r="AO26" s="237" t="n"/>
+      <c r="AP26" s="238" t="n"/>
     </row>
     <row r="27" ht="60" customHeight="1" s="206">
       <c r="A27" s="239">
@@ -4411,7 +4412,7 @@
       </c>
       <c r="C27" s="239" t="inlineStr">
         <is>
-          <t>Quan sát thực tế app STG + ảnh DOC-v1.0-04 (ma trận nhãn nút)</t>
+          <t>DOC-v1.0-04 + DOC-v1.0-05</t>
         </is>
       </c>
       <c r="D27" s="239" t="inlineStr">
@@ -4426,24 +4427,24 @@
       </c>
       <c r="F27" s="239" t="inlineStr">
         <is>
-          <t>Check KHÔNG gửi quà lại lần 2 cho cùng 1 đơn</t>
+          <t>Check nút "Cảm ơn người vận chuyển" đổi thành nhãn "Bạn đã đánh giá" sau khi gửi quà</t>
         </is>
       </c>
       <c r="G27" s="239" t="inlineStr">
         <is>
-          <t>Sender đã gửi quà thành công cho đơn này, nhãn hiện tại là "Bạn đã đánh giá"</t>
+          <t>Sender vừa gửi quà thành công cho 1 đơn đã "Hoàn thành"</t>
         </is>
       </c>
       <c r="H27" s="239" t="inlineStr">
         <is>
-          <t>1. Mở app FoxEco bằng tài khoản Sender, mở đơn đã "Hoàn thành" và ĐÃ tặng quà trước đó
-2. Bấm thử vào nhãn "Bạn đã đánh giá" ở đáy màn Theo dõi đơn
-3. Quan sát kết quả sau khi bấm</t>
+          <t>1. Mở app FoxEco bằng tài khoản Sender, mở đơn đã "Hoàn thành" và gửi quà thành công
+2. Quay lại màn "Theo dõi đơn" của chính đơn vừa tặng quà
+3. Quan sát nút hành động ở đáy màn</t>
         </is>
       </c>
       <c r="I27" s="239" t="inlineStr">
         <is>
-          <t>3. Nhãn KHÔNG phản hồi — không mở lại màn Tặng quà, không phát sinh thêm bản ghi quà nào cho đơn này</t>
+          <t>3. Nút "✓ Cảm ơn người vận chuyển" đã đổi thành nhãn "Bạn đã đánh giá" ở trạng thái disable</t>
         </is>
       </c>
       <c r="J27" s="239" t="inlineStr">
@@ -4488,66 +4489,128 @@
       <c r="AK27" s="240" t="n"/>
       <c r="AL27" s="240" t="n"/>
       <c r="AM27" s="241">
+        <f>IF($A26="","",IF(OR($N26="Yes",$S26="Yes",$X26="Yes",$AC26="Yes",$AH26="Yes"),"Yes","No"))</f>
+        <v/>
+      </c>
+      <c r="AN27" s="241">
+        <f>IF($A26="","",IFERROR(IF($AI26&lt;&gt;"",$AI26,IF($AD26&lt;&gt;"",$AD26,IF($Y26&lt;&gt;"",$Y26,IF($T26&lt;&gt;"",$T26,IF($O26&lt;&gt;"",$O26,""))))),""))</f>
+        <v/>
+      </c>
+      <c r="AO27" s="241">
+        <f>IFERROR(IF($AJ26&lt;&gt;"",$AJ26,IF($AE26&lt;&gt;"",$AE26,IF($Z26&lt;&gt;"",$Z26,IF($U26&lt;&gt;"",$U26,IF($P26&lt;&gt;"",$P26,""))))),"")</f>
+        <v/>
+      </c>
+      <c r="AP27" s="240" t="inlineStr">
+        <is>
+          <t>Technique: ST-gift-not-sent → gift-sent (đổi trạng thái nút sau hành động gửi quà)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="60" customHeight="1" s="206">
+      <c r="A28" s="239">
+        <f>IF(C28="","",$C$2&amp;"."&amp;COUNTA($C$8:C28)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="B28" s="239" t="inlineStr">
+        <is>
+          <t>REQ-GIFT-003</t>
+        </is>
+      </c>
+      <c r="C28" s="239" t="inlineStr">
+        <is>
+          <t>DOC-v1.0-04 + DOC-v1.0-05</t>
+        </is>
+      </c>
+      <c r="D28" s="239" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E28" s="239" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F28" s="239" t="inlineStr">
+        <is>
+          <t>Check KHÔNG gửi quà lại lần 2 cho cùng 1 đơn</t>
+        </is>
+      </c>
+      <c r="G28" s="239" t="inlineStr">
+        <is>
+          <t>Sender đã gửi quà thành công cho đơn này, nhãn hiện tại là "Bạn đã đánh giá"</t>
+        </is>
+      </c>
+      <c r="H28" s="239" t="inlineStr">
+        <is>
+          <t>1. Mở app FoxEco bằng tài khoản Sender, mở đơn đã "Hoàn thành" và ĐÃ tặng quà trước đó
+2. Bấm thử vào nhãn "Bạn đã đánh giá" ở đáy màn Theo dõi đơn
+3. Quan sát kết quả sau khi bấm</t>
+        </is>
+      </c>
+      <c r="I28" s="239" t="inlineStr">
+        <is>
+          <t>3. Nhãn KHÔNG phản hồi — không mở lại màn Tặng quà, không phát sinh thêm bản ghi quà nào cho đơn này</t>
+        </is>
+      </c>
+      <c r="J28" s="239" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="K28" s="239" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="L28" s="239" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M28" s="239" t="n"/>
+      <c r="N28" s="239" t="n"/>
+      <c r="O28" s="239" t="n"/>
+      <c r="P28" s="239" t="n"/>
+      <c r="Q28" s="239" t="n"/>
+      <c r="R28" s="239" t="n"/>
+      <c r="S28" s="239" t="n"/>
+      <c r="T28" s="239" t="n"/>
+      <c r="U28" s="239" t="n"/>
+      <c r="V28" s="239" t="n"/>
+      <c r="W28" s="239" t="n"/>
+      <c r="X28" s="239" t="n"/>
+      <c r="Y28" s="239" t="n"/>
+      <c r="Z28" s="239" t="n"/>
+      <c r="AA28" s="239" t="n"/>
+      <c r="AB28" s="240" t="n"/>
+      <c r="AC28" s="240" t="n"/>
+      <c r="AD28" s="240" t="n"/>
+      <c r="AE28" s="240" t="n"/>
+      <c r="AF28" s="240" t="n"/>
+      <c r="AG28" s="240" t="n"/>
+      <c r="AH28" s="240" t="n"/>
+      <c r="AI28" s="240" t="n"/>
+      <c r="AJ28" s="240" t="n"/>
+      <c r="AK28" s="240" t="n"/>
+      <c r="AL28" s="240" t="n"/>
+      <c r="AM28" s="241">
         <f>IF($A27="","",IF(OR($N27="Yes",$S27="Yes",$X27="Yes",$AC27="Yes",$AH27="Yes"),"Yes","No"))</f>
         <v/>
       </c>
-      <c r="AN27" s="241">
+      <c r="AN28" s="241">
         <f>IF($A27="","",IFERROR(IF($AI27&lt;&gt;"",$AI27,IF($AD27&lt;&gt;"",$AD27,IF($Y27&lt;&gt;"",$Y27,IF($T27&lt;&gt;"",$T27,IF($O27&lt;&gt;"",$O27,""))))),""))</f>
         <v/>
       </c>
-      <c r="AO27" s="241">
+      <c r="AO28" s="241">
         <f>IFERROR(IF($AJ27&lt;&gt;"",$AJ27,IF($AE27&lt;&gt;"",$AE27,IF($Z27&lt;&gt;"",$Z27,IF($U27&lt;&gt;"",$U27,IF($P27&lt;&gt;"",$P27,""))))),"")</f>
         <v/>
       </c>
-      <c r="AP27" s="240" t="inlineStr">
+      <c r="AP28" s="240" t="inlineStr">
         <is>
           <t>Technique: ST-invalid-regift (transition không hợp lệ từ state đã-gửi-quà)</t>
         </is>
       </c>
-    </row>
-    <row r="28" s="206">
-      <c r="A28" s="231" t="n"/>
-      <c r="B28" s="231" t="n"/>
-      <c r="C28" s="231" t="n"/>
-      <c r="D28" s="231" t="n"/>
-      <c r="E28" s="231" t="n"/>
-      <c r="F28" s="249" t="n"/>
-      <c r="G28" s="249" t="n"/>
-      <c r="H28" s="249" t="n"/>
-      <c r="I28" s="249" t="n"/>
-      <c r="J28" s="231" t="n"/>
-      <c r="K28" s="231" t="n"/>
-      <c r="L28" s="231" t="n"/>
-      <c r="M28" s="231" t="n"/>
-      <c r="N28" s="235" t="n"/>
-      <c r="O28" s="235" t="n"/>
-      <c r="P28" s="235" t="n"/>
-      <c r="Q28" s="235" t="n"/>
-      <c r="R28" s="235" t="n"/>
-      <c r="S28" s="235" t="n"/>
-      <c r="T28" s="235" t="n"/>
-      <c r="U28" s="235" t="n"/>
-      <c r="V28" s="235" t="n"/>
-      <c r="W28" s="235" t="n"/>
-      <c r="X28" s="235" t="n"/>
-      <c r="Y28" s="235" t="n"/>
-      <c r="Z28" s="235" t="n"/>
-      <c r="AA28" s="235" t="n"/>
-      <c r="AB28" s="236" t="n"/>
-      <c r="AC28" s="236" t="n"/>
-      <c r="AD28" s="236" t="n"/>
-      <c r="AE28" s="236" t="n"/>
-      <c r="AF28" s="236" t="n"/>
-      <c r="AG28" s="236" t="n"/>
-      <c r="AH28" s="236" t="n"/>
-      <c r="AI28" s="236" t="n"/>
-      <c r="AJ28" s="236" t="n"/>
-      <c r="AK28" s="236" t="n"/>
-      <c r="AL28" s="236" t="n"/>
-      <c r="AM28" s="237" t="n"/>
-      <c r="AN28" s="237" t="n"/>
-      <c r="AO28" s="237" t="n"/>
-      <c r="AP28" s="238" t="n"/>
     </row>
     <row r="29" s="206">
       <c r="A29" s="231" t="n"/>
@@ -19905,17 +19968,17 @@
   <autoFilter ref="A6:U6"/>
   <mergeCells count="24">
     <mergeCell ref="A7:I7"/>
-    <mergeCell ref="B25:I25"/>
     <mergeCell ref="AH5:AL5"/>
     <mergeCell ref="C2:E2"/>
+    <mergeCell ref="B21:I21"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="B11:I11"/>
     <mergeCell ref="AC5:AG5"/>
     <mergeCell ref="J5:M5"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="G3:H3"/>
+    <mergeCell ref="B8:I8"/>
     <mergeCell ref="N5:R5"/>
-    <mergeCell ref="B8:I8"/>
     <mergeCell ref="I3:J3"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="D5:I5"/>
@@ -19925,9 +19988,9 @@
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="I4:J4"/>
     <mergeCell ref="AM5:AP5"/>
-    <mergeCell ref="B20:I20"/>
     <mergeCell ref="S5:W5"/>
     <mergeCell ref="C4:E4"/>
+    <mergeCell ref="B26:I26"/>
   </mergeCells>
   <dataValidations count="8">
     <dataValidation sqref="J8:J17 J19:J502" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
@@ -20255,64 +20318,129 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="254" t="inlineStr">
+        <is>
+          <t>SC-GIFT-008</t>
+        </is>
+      </c>
+      <c r="B5" s="254" t="inlineStr">
+        <is>
+          <t>Icon quay lại tại màn Tặng quà</t>
+        </is>
+      </c>
+      <c r="C5" s="254" t="inlineStr">
+        <is>
+          <t>Quan sát thực tế app STG (QA GiangDC2, chat 2026-07-30)</t>
+        </is>
+      </c>
+      <c r="D5" s="255" t="inlineStr">
+        <is>
+          <t>N/A: display/navigation-only, không có input/condition để áp dụng technique</t>
+        </is>
+      </c>
+      <c r="E5" s="256" t="inlineStr">
+        <is>
+          <t>N/A: display/navigation-only, không có input/condition để áp dụng technique</t>
+        </is>
+      </c>
+      <c r="F5" s="256" t="inlineStr">
+        <is>
+          <t>N/A: display/navigation-only, không có input/condition để áp dụng technique</t>
+        </is>
+      </c>
+      <c r="G5" s="255" t="inlineStr">
+        <is>
+          <t>N/A: display/navigation-only, không có input/condition để áp dụng technique</t>
+        </is>
+      </c>
+      <c r="H5" s="256" t="inlineStr">
+        <is>
+          <t>N/A: display/navigation-only, không có input/condition để áp dụng technique</t>
+        </is>
+      </c>
+      <c r="I5" s="256" t="inlineStr">
+        <is>
+          <t>N/A: display/navigation-only, không có input/condition để áp dụng technique</t>
+        </is>
+      </c>
+      <c r="J5" s="256" t="inlineStr">
+        <is>
+          <t>N/A: display/navigation-only, không có input/condition để áp dụng technique</t>
+        </is>
+      </c>
+      <c r="K5" s="256" t="inlineStr">
+        <is>
+          <t>N/A: display/navigation-only, không có input/condition để áp dụng technique</t>
+        </is>
+      </c>
+      <c r="L5" s="254" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" s="255" t="inlineStr">
+        <is>
+          <t>100% (2/2)</t>
+        </is>
+      </c>
+    </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="205" t="inlineStr">
         <is>
           <t>Total scenarios: 3 (SC-GIFT-001/002/004 — 4 scenario GIFT còn lại SC-GIFT-003/005/006/007 đã cover tại TC-CANHAN)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Total TCs derived: 16</t>
+      <c r="A7" s="205" t="inlineStr">
+        <is>
+          <t>Total TCs derived: 17</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="205" t="inlineStr">
         <is>
           <t>Average coverage %: 100% trên 2/3 scenario có technique applicable; SC-GIFT-002 log N/A (0 applicable) vì mọi dimension đã dedupe sang 2 scenario còn lại</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="205" t="inlineStr">
         <is>
           <t>Most-applied technique: B1 EP (7 TC)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="205" t="inlineStr">
         <is>
           <t>Least-applied technique: B4 ST (2 TC) — B2 BVA / B3 DT / B5 PW / B6 EG / B7 CRUD / B8 CEG N/A toàn module</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="205" t="inlineStr">
         <is>
           <t>Ghi chú Step 3b: 3 TC completeness — màn Tặng quà (5 thành phần), danh sách 4 chip loại quà, popup "Đã gửi lời cảm ơn!" (3 thành phần). Cả 3 verbatim từ ảnh Figma DOC-v1.0-04.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="205" t="inlineStr">
         <is>
           <t>Ghi chú ma trận nhãn nút: ô cuối cùng (hàng "Hoàn thành" × cột Người gửi) được cover tại đây — 14 ô còn lại đã cover ở TC-THEODOIDON (11 ô) và TC-BANGTIN (3 ô cột Carrier hàng "Chờ ghép", tại màn Chi tiết tin). Ma trận 15 ô nay đủ 15/15.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="205" t="inlineStr">
         <is>
           <t>Ghi chú out of scope: KHÔNG derive TC cho REQ-GIFT-002 (chấm sao 1-5, RAT-01/02) — C-GIFT-01 Resolved/Deferred, phase sau; màn Tặng quà xác nhận KHÔNG có UI sao.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="205" t="inlineStr">
         <is>
           <t>Ghi chú rubric: chạy auto-apply (non-interactive) toàn bộ technique applicable theo technique-rubric.md; không technique applicable nào bị bỏ qua.</t>
         </is>

--- a/03_test-cases/v1.0/fragments/TC-TANGQUA-v1.0.xlsx
+++ b/03_test-cases/v1.0/fragments/TC-TANGQUA-v1.0.xlsx
@@ -2945,7 +2945,7 @@
       </c>
       <c r="C12" s="239" t="inlineStr">
         <is>
-          <t>Quan sát thực tế app STG (QA GiangDC2, chat 2026-07-30)</t>
+          <t>DOC-v1.0-05</t>
         </is>
       </c>
       <c r="D12" s="239" t="inlineStr">
